--- a/Книга1.xlsx
+++ b/Книга1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\4_Тимофей\проект\личное\data-transformer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E4A5E27-0015-4875-87FF-0D5A1D8FECBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71986179-EBA0-4E57-858A-AA1C36B354C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{FA1D215A-A707-4EAD-881B-68F78903503C}"/>
+    <workbookView xWindow="-105" yWindow="10440" windowWidth="19545" windowHeight="10545" xr2:uid="{FA1D215A-A707-4EAD-881B-68F78903503C}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -25,19 +25,22 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>Общий вид</t>
   </si>
   <si>
     <t>Схема</t>
   </si>
+  <si>
+    <t>2 3</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -53,6 +56,15 @@
       <family val="1"/>
       <charset val="204"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -62,7 +74,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -262,17 +274,27 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="dotted">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
@@ -285,10 +307,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -830,14 +856,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>95250</xdr:colOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>66675</xdr:colOff>
       <xdr:row>26</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>485775</xdr:colOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>1047750</xdr:colOff>
       <xdr:row>27</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
@@ -854,7 +880,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8477250" y="5067300"/>
+          <a:off x="10820400" y="5067300"/>
           <a:ext cx="981075" cy="304800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1050,7 +1076,7 @@
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>1866901</xdr:colOff>
-      <xdr:row>33</xdr:row>
+      <xdr:row>35</xdr:row>
       <xdr:rowOff>180975</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1109,16 +1135,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>114299</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>19049</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>2600324</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>76199</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1133,8 +1159,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10868024" y="6248400"/>
-          <a:ext cx="2486025" cy="314325"/>
+          <a:off x="8401049" y="6581775"/>
+          <a:ext cx="2428875" cy="695325"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1176,16 +1202,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>123826</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>76201</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>1400176</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>171450</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>1943101</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1200,7 +1226,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8505826" y="6610350"/>
+          <a:off x="10829926" y="6619875"/>
           <a:ext cx="1866900" cy="314325"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1244,14 +1270,14 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>180975</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>57150</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>32</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1267,7 +1293,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13477875" y="5314950"/>
+          <a:off x="13420725" y="5505450"/>
           <a:ext cx="2305050" cy="790575"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1619,7 +1645,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBD75EFD-CD06-4E9B-93EA-3F9C0CD6A209}">
-  <dimension ref="D3:T37"/>
+  <dimension ref="F3:R39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="5" max="5" width="9.42578125" customWidth="1"/>
@@ -1634,7 +1660,7 @@
   </cols>
   <sheetData>
     <row r="3" spans="6:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="F3" s="10" t="s">
+      <c r="F3" s="9" t="s">
         <v>0</v>
       </c>
     </row>
@@ -1646,10 +1672,10 @@
       <c r="I5" s="3"/>
     </row>
     <row r="6" spans="6:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F6" s="7"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="9"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="8"/>
     </row>
     <row r="7" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F7" s="1"/>
@@ -1659,392 +1685,212 @@
     </row>
     <row r="8" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F8" s="4"/>
-      <c r="G8" s="5"/>
       <c r="H8" s="4"/>
-      <c r="I8" s="6"/>
+      <c r="I8" s="5"/>
     </row>
     <row r="9" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F9" s="4"/>
-      <c r="G9" s="5"/>
       <c r="H9" s="4"/>
-      <c r="I9" s="6"/>
+      <c r="I9" s="5"/>
     </row>
     <row r="10" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F10" s="4"/>
-      <c r="G10" s="5"/>
       <c r="H10" s="4"/>
-      <c r="I10" s="6"/>
+      <c r="I10" s="5"/>
     </row>
     <row r="11" spans="6:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F11" s="7"/>
-      <c r="G11" s="8"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="7"/>
       <c r="H11" s="4"/>
-      <c r="I11" s="6"/>
+      <c r="I11" s="5"/>
     </row>
     <row r="12" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F12" s="4"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="5"/>
-      <c r="I12" s="6"/>
+      <c r="G12" s="5"/>
+      <c r="I12" s="5"/>
     </row>
     <row r="13" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F13" s="4"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="5"/>
-      <c r="I13" s="6"/>
+      <c r="G13" s="5"/>
+      <c r="I13" s="5"/>
     </row>
     <row r="14" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F14" s="4"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="5"/>
-      <c r="I14" s="6"/>
+      <c r="G14" s="5"/>
+      <c r="I14" s="5"/>
     </row>
     <row r="15" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F15" s="4"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="5"/>
-      <c r="I15" s="6"/>
+      <c r="G15" s="5"/>
+      <c r="I15" s="5"/>
     </row>
     <row r="16" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F16" s="4"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="5"/>
-      <c r="I16" s="6"/>
-    </row>
-    <row r="17" spans="4:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F17" s="7"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="8"/>
-      <c r="I17" s="9"/>
-    </row>
-    <row r="18" spans="4:20" x14ac:dyDescent="0.25">
-      <c r="F18" s="5"/>
-      <c r="G18" s="5"/>
-      <c r="H18" s="5"/>
-      <c r="I18" s="5"/>
-      <c r="L18" s="5"/>
-      <c r="M18" s="5"/>
-      <c r="N18" s="5"/>
-      <c r="O18" s="5"/>
-      <c r="P18" s="5"/>
-      <c r="Q18" s="5"/>
-      <c r="R18" s="5"/>
-      <c r="S18" s="5"/>
-      <c r="T18" s="5"/>
-    </row>
-    <row r="19" spans="4:20" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="E19" s="5"/>
-      <c r="F19" s="18"/>
-      <c r="G19" s="5"/>
-      <c r="H19" s="5"/>
-      <c r="I19" s="5"/>
-      <c r="J19" s="5"/>
-      <c r="L19" s="18" t="s">
+      <c r="G16" s="5"/>
+      <c r="I16" s="5"/>
+    </row>
+    <row r="17" spans="6:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F17" s="6"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="7"/>
+      <c r="I17" s="8"/>
+    </row>
+    <row r="19" spans="6:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F19" s="9"/>
+      <c r="L19" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="M19" s="18"/>
-      <c r="N19" s="5"/>
-      <c r="O19" s="5"/>
-      <c r="P19" s="5"/>
-      <c r="Q19" s="5"/>
-      <c r="R19" s="5"/>
-      <c r="S19" s="5"/>
-      <c r="T19" s="5"/>
-    </row>
-    <row r="20" spans="4:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
-      <c r="G20" s="5"/>
-      <c r="H20" s="5"/>
-      <c r="I20" s="5"/>
-      <c r="J20" s="5"/>
-      <c r="L20" s="8"/>
-      <c r="M20" s="8"/>
-      <c r="N20" s="8"/>
-      <c r="P20" s="5"/>
-      <c r="Q20" s="5"/>
-      <c r="R20" s="5"/>
-      <c r="S20" s="5"/>
-      <c r="T20" s="5"/>
-    </row>
-    <row r="21" spans="4:20" x14ac:dyDescent="0.25">
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="5"/>
-      <c r="H21" s="5"/>
-      <c r="I21" s="5"/>
-      <c r="J21" s="5"/>
+      <c r="M19" s="9"/>
+    </row>
+    <row r="20" spans="6:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L20" s="7"/>
+      <c r="M20" s="7"/>
+      <c r="N20" s="7"/>
+    </row>
+    <row r="21" spans="6:16" x14ac:dyDescent="0.25">
       <c r="L21" s="1"/>
-      <c r="M21" s="19"/>
-      <c r="N21" s="19"/>
+      <c r="M21" s="17"/>
+      <c r="N21" s="17"/>
       <c r="O21" s="3"/>
-      <c r="P21" s="5">
+      <c r="P21">
         <v>1</v>
       </c>
-      <c r="Q21" s="5"/>
-      <c r="R21" s="5"/>
-      <c r="S21" s="5"/>
-      <c r="T21" s="5"/>
-    </row>
-    <row r="22" spans="4:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
-      <c r="G22" s="5"/>
-      <c r="H22" s="5"/>
-      <c r="I22" s="5"/>
-      <c r="J22" s="5"/>
-      <c r="L22" s="7"/>
-      <c r="M22" s="15"/>
-      <c r="N22" s="15"/>
-      <c r="O22" s="9"/>
-      <c r="P22" s="5"/>
-      <c r="Q22" s="5"/>
-      <c r="R22" s="5"/>
-      <c r="S22" s="5"/>
-      <c r="T22" s="5"/>
-    </row>
-    <row r="23" spans="4:20" x14ac:dyDescent="0.25">
-      <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
-      <c r="G23" s="5"/>
-      <c r="H23" s="5"/>
-      <c r="I23" s="5"/>
-      <c r="J23" s="5"/>
-      <c r="L23" s="4"/>
-      <c r="M23" s="13"/>
-      <c r="N23" s="5"/>
-      <c r="O23" s="20"/>
-      <c r="P23" s="5">
+    </row>
+    <row r="22" spans="6:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L22" s="6"/>
+      <c r="M22" s="14"/>
+      <c r="N22" s="14"/>
+      <c r="O22" s="8"/>
+      <c r="P22">
         <v>2</v>
       </c>
-      <c r="Q23" s="5"/>
-      <c r="R23" s="5"/>
-      <c r="S23" s="5"/>
-      <c r="T23" s="5"/>
-    </row>
-    <row r="24" spans="4:20" x14ac:dyDescent="0.25">
-      <c r="E24" s="5"/>
-      <c r="F24" s="5"/>
-      <c r="G24" s="5"/>
-      <c r="H24" s="5"/>
-      <c r="I24" s="5"/>
-      <c r="J24" s="5"/>
-      <c r="L24" s="11"/>
-      <c r="M24" s="14"/>
-      <c r="N24" s="12"/>
-      <c r="O24" s="21"/>
-      <c r="P24" s="5"/>
-      <c r="Q24" s="5"/>
-      <c r="R24" s="5"/>
-      <c r="S24" s="5"/>
-      <c r="T24" s="5"/>
-    </row>
-    <row r="25" spans="4:20" x14ac:dyDescent="0.25">
-      <c r="E25" s="5"/>
-      <c r="F25" s="5"/>
-      <c r="G25" s="5"/>
-      <c r="H25" s="5"/>
-      <c r="I25" s="5"/>
-      <c r="J25" s="5"/>
-      <c r="L25" s="4"/>
-      <c r="M25" s="13"/>
-      <c r="N25" s="5"/>
-      <c r="O25" s="17"/>
-      <c r="P25" s="5">
+    </row>
+    <row r="23" spans="6:16" x14ac:dyDescent="0.25">
+      <c r="L23" s="4"/>
+      <c r="M23" s="12"/>
+      <c r="O23" s="18"/>
+      <c r="P23">
         <v>3</v>
       </c>
-      <c r="Q25" s="5"/>
-      <c r="R25" s="5"/>
-      <c r="S25" s="5"/>
-      <c r="T25" s="5"/>
-    </row>
-    <row r="26" spans="4:20" x14ac:dyDescent="0.25">
-      <c r="E26" s="5"/>
-      <c r="F26" s="5"/>
-      <c r="G26" s="5"/>
-      <c r="H26" s="5"/>
-      <c r="I26" s="5"/>
-      <c r="J26" s="5"/>
-      <c r="L26" s="11"/>
-      <c r="M26" s="14"/>
-      <c r="N26" s="12"/>
-      <c r="O26" s="21"/>
-      <c r="P26" s="5"/>
-      <c r="Q26" s="5"/>
-      <c r="R26" s="5"/>
-      <c r="S26" s="5"/>
-      <c r="T26" s="5"/>
-    </row>
-    <row r="27" spans="4:20" x14ac:dyDescent="0.25">
-      <c r="E27" s="5"/>
-      <c r="F27" s="5"/>
-      <c r="G27" s="5"/>
-      <c r="H27" s="5"/>
-      <c r="I27" s="5"/>
-      <c r="J27" s="5"/>
-      <c r="L27" s="4"/>
-      <c r="M27" s="13"/>
-      <c r="N27" s="5"/>
-      <c r="O27" s="17"/>
-      <c r="P27" s="5">
+    </row>
+    <row r="24" spans="6:16" x14ac:dyDescent="0.25">
+      <c r="L24" s="10"/>
+      <c r="M24" s="13"/>
+      <c r="N24" s="11"/>
+      <c r="O24" s="19"/>
+    </row>
+    <row r="25" spans="6:16" x14ac:dyDescent="0.25">
+      <c r="L25" s="4"/>
+      <c r="M25" s="12"/>
+      <c r="O25" s="16"/>
+      <c r="P25">
         <v>4</v>
       </c>
-      <c r="Q27" s="5"/>
-      <c r="R27" s="5"/>
-      <c r="S27" s="5"/>
-      <c r="T27" s="5"/>
-    </row>
-    <row r="28" spans="4:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E28" s="5"/>
-      <c r="F28" s="5"/>
-      <c r="G28" s="5"/>
-      <c r="H28" s="5"/>
-      <c r="I28" s="5"/>
-      <c r="J28" s="5"/>
-      <c r="L28" s="4"/>
-      <c r="M28" s="13"/>
-      <c r="N28" s="5"/>
-      <c r="O28" s="21"/>
-      <c r="P28" s="5"/>
-      <c r="Q28" s="5"/>
-      <c r="R28" s="5"/>
-      <c r="S28" s="5"/>
-      <c r="T28" s="5"/>
-    </row>
-    <row r="29" spans="4:20" x14ac:dyDescent="0.25">
-      <c r="E29" s="5"/>
-      <c r="F29" s="5"/>
-      <c r="G29" s="5"/>
-      <c r="H29" s="5"/>
-      <c r="I29" s="5"/>
-      <c r="J29" s="5"/>
-      <c r="L29" s="1"/>
-      <c r="M29" s="19"/>
-      <c r="N29" s="2"/>
-      <c r="O29" s="17"/>
-      <c r="P29" s="5">
+    </row>
+    <row r="26" spans="6:16" x14ac:dyDescent="0.25">
+      <c r="L26" s="10"/>
+      <c r="M26" s="13"/>
+      <c r="N26" s="11"/>
+      <c r="O26" s="19"/>
+    </row>
+    <row r="27" spans="6:16" x14ac:dyDescent="0.25">
+      <c r="L27" s="4"/>
+      <c r="M27" s="12"/>
+      <c r="O27" s="16"/>
+      <c r="P27">
         <v>5</v>
       </c>
-      <c r="Q29" s="5"/>
-      <c r="R29" s="5"/>
-      <c r="S29" s="5"/>
-      <c r="T29" s="5"/>
-    </row>
-    <row r="30" spans="4:20" x14ac:dyDescent="0.25">
-      <c r="E30" s="5"/>
-      <c r="F30" s="5"/>
-      <c r="G30" s="5"/>
-      <c r="H30" s="5"/>
-      <c r="I30" s="5"/>
-      <c r="J30" s="5"/>
-      <c r="L30" s="11"/>
-      <c r="M30" s="14"/>
-      <c r="N30" s="12"/>
-      <c r="O30" s="21"/>
-      <c r="P30" s="5"/>
-      <c r="Q30" s="5"/>
-      <c r="R30" s="5"/>
-      <c r="S30" s="5"/>
-      <c r="T30" s="5"/>
-    </row>
-    <row r="31" spans="4:20" x14ac:dyDescent="0.25">
-      <c r="E31" s="5"/>
-      <c r="F31" s="5"/>
-      <c r="G31" s="5"/>
-      <c r="H31" s="5"/>
-      <c r="I31" s="5"/>
-      <c r="J31" s="5"/>
-      <c r="L31" s="4"/>
-      <c r="M31" s="13"/>
-      <c r="N31" s="5"/>
-      <c r="O31" s="17"/>
-      <c r="P31">
+    </row>
+    <row r="28" spans="6:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L28" s="4"/>
+      <c r="M28" s="12"/>
+      <c r="O28" s="19"/>
+      <c r="P28">
         <v>6</v>
       </c>
     </row>
-    <row r="32" spans="4:20" x14ac:dyDescent="0.25">
-      <c r="E32" s="5"/>
-      <c r="F32" s="5"/>
-      <c r="G32" s="5"/>
-      <c r="H32" s="5"/>
-      <c r="I32" s="5"/>
-      <c r="J32" s="5"/>
-      <c r="L32" s="11"/>
-      <c r="M32" s="14"/>
-      <c r="N32" s="12"/>
-      <c r="O32" s="21"/>
-    </row>
-    <row r="33" spans="5:16" x14ac:dyDescent="0.25">
-      <c r="E33" s="5"/>
-      <c r="F33" s="5"/>
-      <c r="G33" s="5"/>
-      <c r="H33" s="5"/>
-      <c r="I33" s="5"/>
-      <c r="J33" s="5"/>
-      <c r="L33" s="4"/>
-      <c r="M33" s="13"/>
-      <c r="N33" s="5"/>
-      <c r="O33" s="17"/>
-      <c r="P33">
+    <row r="29" spans="6:16" x14ac:dyDescent="0.25">
+      <c r="L29" s="1"/>
+      <c r="M29" s="17"/>
+      <c r="N29" s="2"/>
+      <c r="O29" s="16"/>
+      <c r="P29">
         <v>7</v>
       </c>
     </row>
-    <row r="34" spans="5:16" x14ac:dyDescent="0.25">
-      <c r="E34" s="5"/>
-      <c r="F34" s="5"/>
-      <c r="G34" s="5"/>
-      <c r="H34" s="5"/>
-      <c r="I34" s="5"/>
-      <c r="J34" s="5"/>
-      <c r="L34" s="11"/>
-      <c r="M34" s="14"/>
-      <c r="N34" s="12"/>
-      <c r="O34" s="21"/>
-    </row>
-    <row r="35" spans="5:16" x14ac:dyDescent="0.25">
-      <c r="E35" s="5"/>
-      <c r="F35" s="5"/>
-      <c r="G35" s="5"/>
-      <c r="H35" s="5"/>
-      <c r="I35" s="5"/>
-      <c r="J35" s="5"/>
-      <c r="L35" s="4"/>
-      <c r="M35" s="13"/>
-      <c r="N35" s="5"/>
-      <c r="O35" s="17"/>
-      <c r="P35">
+    <row r="30" spans="6:16" x14ac:dyDescent="0.25">
+      <c r="L30" s="10"/>
+      <c r="M30" s="13"/>
+      <c r="N30" s="11"/>
+      <c r="O30" s="19"/>
+    </row>
+    <row r="31" spans="6:16" x14ac:dyDescent="0.25">
+      <c r="L31" s="4"/>
+      <c r="M31" s="12"/>
+      <c r="O31" s="16"/>
+      <c r="P31">
         <v>8</v>
       </c>
     </row>
-    <row r="36" spans="5:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E36" s="5"/>
-      <c r="F36" s="5"/>
-      <c r="G36" s="5"/>
-      <c r="H36" s="5"/>
-      <c r="I36" s="5"/>
-      <c r="J36" s="5"/>
-      <c r="L36" s="7"/>
-      <c r="M36" s="15"/>
-      <c r="N36" s="8"/>
-      <c r="O36" s="16"/>
-    </row>
-    <row r="37" spans="5:16" x14ac:dyDescent="0.25">
-      <c r="E37" s="5"/>
-      <c r="F37" s="5"/>
-      <c r="G37" s="5"/>
-      <c r="H37" s="5"/>
-      <c r="I37" s="5"/>
-      <c r="J37" s="5"/>
-      <c r="M37">
+    <row r="32" spans="6:16" x14ac:dyDescent="0.25">
+      <c r="L32" s="10"/>
+      <c r="M32" s="13"/>
+      <c r="N32" s="11"/>
+      <c r="O32" s="19"/>
+    </row>
+    <row r="33" spans="12:18" x14ac:dyDescent="0.25">
+      <c r="L33" s="4"/>
+      <c r="M33" s="12"/>
+      <c r="O33" s="16"/>
+      <c r="P33">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="34" spans="12:18" x14ac:dyDescent="0.25">
+      <c r="L34" s="10"/>
+      <c r="M34" s="13"/>
+      <c r="N34" s="21"/>
+      <c r="O34" s="19"/>
+    </row>
+    <row r="35" spans="12:18" x14ac:dyDescent="0.25">
+      <c r="L35" s="4"/>
+      <c r="M35" s="12"/>
+      <c r="O35" s="16"/>
+      <c r="P35">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36" spans="12:18" x14ac:dyDescent="0.25">
+      <c r="L36" s="10"/>
+      <c r="M36" s="13"/>
+      <c r="N36" s="11"/>
+      <c r="O36" s="19"/>
+    </row>
+    <row r="37" spans="12:18" x14ac:dyDescent="0.25">
+      <c r="L37" s="4"/>
+      <c r="M37" s="12"/>
+      <c r="O37" s="16"/>
+      <c r="P37">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="38" spans="12:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L38" s="6"/>
+      <c r="M38" s="14"/>
+      <c r="N38" s="7"/>
+      <c r="O38" s="15"/>
+    </row>
+    <row r="39" spans="12:18" x14ac:dyDescent="0.25">
+      <c r="M39">
         <v>1</v>
       </c>
-      <c r="N37">
+      <c r="N39" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="O37">
-        <v>3</v>
+      <c r="O39">
+        <v>4</v>
       </c>
+      <c r="R39" s="22"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
